--- a/output/pdf_financials_xlsx/NUAG.xlsx
+++ b/output/pdf_financials_xlsx/NUAG.xlsx
@@ -4513,40 +4513,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>17.324178</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>17.512523</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>17.642249</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>17.84538</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>23.440856</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>15.265578</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>16.813906</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>16.564197</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>15.395486</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>18.636297</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>19.931083</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>20.676968</v>
       </c>
     </row>
     <row r="93">
@@ -4796,7 +4796,7 @@
         <v>-2.572755</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>7.912887</v>
+        <v>-7.912887</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-6.574374</v>
@@ -7536,7 +7536,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -13546,7 +13550,11 @@
           <t>Share‐based payment reserve</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr"/>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E100" s="5" t="n">
         <v>17.324178</v>
       </c>
@@ -15420,7 +15428,7 @@
         <v>-2.572755</v>
       </c>
       <c r="K125" s="5" t="n">
-        <v>7.912887</v>
+        <v>-7.912887</v>
       </c>
       <c r="L125" s="5" t="n">
         <v>-6.574374</v>

--- a/output/pdf_financials_xlsx/NUAG.xlsx
+++ b/output/pdf_financials_xlsx/NUAG.xlsx
@@ -898,22 +898,22 @@
         <v>-0.168731</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>-0.202375</v>
+        <v>0.132697</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.047556</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.002541</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.014243</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.040893</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.030024</v>
       </c>
       <c r="I12" s="1" t="inlineStr">
         <is>
@@ -1653,22 +1653,22 @@
         <v>-41.384076</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>1.911379</v>
+        <v>1.576307</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.809907</v>
+        <v>-0.857463</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>1.354527</v>
+        <v>1.351986</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-4.122185</v>
+        <v>-4.136428</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.572755</v>
+        <v>-2.613648</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>7.912887</v>
+        <v>7.882863</v>
       </c>
       <c r="I27" s="1" t="inlineStr">
         <is>
@@ -1743,22 +1743,22 @@
         <v>-41.324884</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>1.950631</v>
+        <v>1.615559</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.769396</v>
+        <v>-0.816952</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>1.386728</v>
+        <v>1.384187</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4.104203</v>
+        <v>-4.118446</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-2.560756</v>
+        <v>-2.601649</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>7.924882</v>
+        <v>7.894858</v>
       </c>
       <c r="I29" s="1" t="inlineStr">
         <is>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>963.8695491043854</v>
+        <v>798.2996911673872</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-24.83026325895834</v>
+        <v>-26.36500999476542</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -1801,13 +1801,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>266.5484014056746</v>
+        <v>267.4734162943682</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-167.1085251740581</v>
+        <v>-169.7770999699163</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>449.8903783904074</v>
+        <v>448.1859355077507</v>
       </c>
       <c r="I30" s="1" t="inlineStr">
         <is>
@@ -1966,19 +1966,19 @@
         <v>14.604113</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>27.849961</v>
+        <v>21.280631</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>40.644346</v>
+        <v>29.824146</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>46.441482</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>29.322504</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>6.296312</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>21.950211</v>
@@ -2052,19 +2052,19 @@
         <v>14.604113</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>36.211616</v>
+        <v>29.642286</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>55.785065</v>
+        <v>44.964865</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.143914</v>
+        <v>46.585396</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.192398</v>
+        <v>29.514902</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.198375</v>
+        <v>6.494687</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>22.208913</v>
@@ -2568,19 +2568,19 @@
         <v>18.186566</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0</v>
+        <v>0.108787</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0</v>
+        <v>8.858812</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>46.964623</v>
+        <v>0.523141</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>29.80177</v>
+        <v>0.479266</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>6.927714</v>
+        <v>0.631402</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.338824</v>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -11472,7 +11472,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E72" t="inlineStr">
         <is>
           <t>-</t>
@@ -12744,7 +12748,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E89" s="5" t="n">
         <v>0.015075</v>
       </c>
@@ -32564,7 +32572,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
@@ -35086,7 +35094,7 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
@@ -35922,7 +35930,7 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">

--- a/output/pdf_financials_xlsx/NUAG.xlsx
+++ b/output/pdf_financials_xlsx/NUAG.xlsx
@@ -3394,40 +3394,40 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.259685</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.247994</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.17578</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.188198</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.229135</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.160903</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.7038140000000001</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.417506</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>1.40467</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.889028</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.588568</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.593271</v>
       </c>
     </row>
     <row r="68">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.988798</v>
+        <v>1.248483</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>1.292765</v>
+        <v>1.540759</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>0.701228</v>
@@ -3449,7 +3449,7 @@
         <v>0.355909</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>1.82735</v>
+        <v>2.056485</v>
       </c>
       <c r="G68" s="3" t="n">
         <v>1.238944</v>
@@ -5091,28 +5091,28 @@
         <v>-0.357177</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>1.313755</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-0.287152</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-0.094231</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>-0.558356</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>0.9258</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-1.086144</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>-0.403717</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>0.16528</v>
       </c>
     </row>
     <row r="107">
@@ -5337,13 +5337,13 @@
         </is>
       </c>
       <c r="B112" s="3" t="n">
-        <v>0</v>
+        <v>0.010673</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.02321</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.11055</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -15920,7 +15920,11 @@
           <t>Changes in non-cash operating working capital 16</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -20402,7 +20406,11 @@
           <t>Changes in non-cash operating working capital 17</t>
         </is>
       </c>
-      <c r="D192" t="inlineStr"/>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E192" t="inlineStr">
         <is>
           <t>-</t>
@@ -21578,7 +21586,11 @@
           <t>Changes in non-cash operating working capital 18</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -24034,7 +24046,11 @@
           <t>Changes in non‐cash operating working capital 18</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -24856,7 +24872,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr"/>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E252" s="5" t="n">
         <v>-41.552807</v>
       </c>
@@ -27412,7 +27432,11 @@
           <t>Proceeds from disposition of plant and equipment</t>
         </is>
       </c>
-      <c r="D286" t="inlineStr"/>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>-</t>
@@ -28690,7 +28714,11 @@
           <t>Proceeds from disposition of plant and equipment</t>
         </is>
       </c>
-      <c r="D303" t="inlineStr"/>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E303" s="5" t="n">
         <v>0.010673</v>
       </c>
